--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486416_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486416_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.569</v>
+        <v>2.7186</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8326</v>
+        <v>0.9205</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7365</v>
+        <v>1.7981</v>
       </c>
       <c r="G2" t="n">
         <v>-2.2658</v>
@@ -610,13 +610,13 @@
         <v>3.4801</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2248</v>
+        <v>0.3743</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4048</v>
+        <v>0.4927</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.18</v>
+        <v>-0.1184</v>
       </c>
       <c r="V2" t="n">
         <v>1.13</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.666</v>
+        <v>2.1623</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.2535</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7239</v>
+        <v>1.9089</v>
       </c>
       <c r="G3" t="n">
         <v>1.0165</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5619</v>
+        <v>0.0583</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7367</v>
+        <v>0.0481</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1747</v>
+        <v>0.0102</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9905</v>
+        <v>1.8075</v>
       </c>
       <c r="E4" t="n">
-        <v>1.755</v>
+        <v>-1.2334</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2355</v>
+        <v>3.0409</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7311</v>
+        <v>-0.1019</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5663</v>
+        <v>0.7117</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8351</v>
+        <v>-0.8136</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1688</v>
+        <v>-1.3066</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9011</v>
+        <v>0.3166</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2677</v>
+        <v>-1.6232</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4377</v>
+        <v>1.2047</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3348</v>
+        <v>0.3951</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1029</v>
+        <v>0.8096</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1751</v>
+        <v>3.0451</v>
       </c>
       <c r="S4" t="n">
-        <v>0.584</v>
+        <v>-0.3957</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3257</v>
+        <v>-0.5119</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2584</v>
+        <v>0.1163</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.4997</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7395</v>
+        <v>1.8902</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7602</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5489</v>
+        <v>1.6118</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9544</v>
+        <v>1.3435</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5032</v>
+        <v>0.2683</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1019</v>
+        <v>3.3131</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7117</v>
+        <v>-0.7087</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8136</v>
+        <v>4.0218</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.3066</v>
+        <v>5.0027</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3166</v>
+        <v>-0.3555</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.6232</v>
+        <v>5.3581</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2047</v>
+        <v>-1.6896</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3951</v>
+        <v>-0.3532</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8096</v>
+        <v>-1.3364</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.305</v>
+        <v>-3.4801</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0451</v>
+        <v>3.9151</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6543</v>
+        <v>-0.4413</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2329</v>
+        <v>-0.179</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5786</v>
+        <v>-0.2623</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5649999999999999</v>
+        <v>-1.695</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3252</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1404</v>
+        <v>1.5705</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0263</v>
+        <v>1.6432</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1142</v>
+        <v>-0.0727</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3131</v>
+        <v>0.7311</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7087</v>
+        <v>1.5663</v>
       </c>
       <c r="I6" t="n">
-        <v>4.0218</v>
+        <v>-0.8351</v>
       </c>
       <c r="J6" t="n">
-        <v>5.0027</v>
+        <v>2.1688</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3555</v>
+        <v>1.9011</v>
       </c>
       <c r="L6" t="n">
-        <v>5.3581</v>
+        <v>0.2677</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6896</v>
+        <v>-1.4377</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3532</v>
+        <v>-0.3348</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3364</v>
+        <v>-1.1029</v>
       </c>
       <c r="P6" t="n">
-        <v>0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4801</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.9151</v>
+        <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9127</v>
+        <v>0.164</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4963</v>
+        <v>0.2139</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4164</v>
+        <v>-0.0499</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.695</v>
+        <v>-1.4997</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.695</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6381</v>
+        <v>-0.055</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0897</v>
+        <v>-2.6606</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4516</v>
+        <v>2.6057</v>
       </c>
       <c r="G7" t="n">
         <v>1.5587</v>
@@ -1000,13 +1000,13 @@
         <v>3.2626</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6748</v>
+        <v>-0.0916</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5564</v>
+        <v>-0.1274</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1184</v>
+        <v>0.0357</v>
       </c>
       <c r="V7" t="n">
         <v>-1.3045</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8652</v>
+        <v>-0.4729</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7657</v>
+        <v>-1.2501</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9005</v>
+        <v>0.7772</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9595</v>
@@ -1078,13 +1078,13 @@
         <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4728</v>
+        <v>-0.0805</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4795</v>
+        <v>0.0361</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0067</v>
+        <v>-0.1166</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9554</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0413</v>
+        <v>-1.6873</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.7285</v>
+        <v>-4.4978</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6872</v>
+        <v>2.8105</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1444</v>
@@ -1156,13 +1156,13 @@
         <v>2.8276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6592</v>
+        <v>-0.3052</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4879</v>
+        <v>-0.2572</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1714</v>
+        <v>-0.0481</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7602</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7319</v>
+        <v>-3.2927</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9725</v>
+        <v>-2.749</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7594</v>
+        <v>-0.5437</v>
       </c>
       <c r="G10" t="n">
         <v>-4.6569</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8151</v>
+        <v>-0.3758</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2824</v>
+        <v>-0.0589</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5327</v>
+        <v>-0.317</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5782</v>
+        <v>-5.5904</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4859</v>
+        <v>-4.4981</v>
       </c>
       <c r="F11" t="n">
         <v>-1.0923</v>
@@ -1312,10 +1312,10 @@
         <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4865</v>
+        <v>-0.4987</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2329</v>
+        <v>-0.2451</v>
       </c>
       <c r="U11" t="n">
         <v>-0.2536</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9399</v>
+        <v>-1.2276</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.4408</v>
+        <v>-12.7283</v>
       </c>
       <c r="F12" t="n">
         <v>11.5009</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.9483</v>
+        <v>-5.948300000000001</v>
       </c>
       <c r="H12" t="n">
         <v>-2.6453</v>
@@ -1363,10 +1363,10 @@
         <v>-3.3029</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.715800000000001</v>
+        <v>-2.7158</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.114400000000001</v>
+        <v>-3.1144</v>
       </c>
       <c r="L12" t="n">
         <v>0.3985000000000003</v>
@@ -1375,7 +1375,7 @@
         <v>-3.2326</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4689999999999998</v>
+        <v>0.469</v>
       </c>
       <c r="O12" t="n">
         <v>-3.7016</v>
@@ -1390,16 +1390,16 @@
         <v>25.01329999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.3047</v>
+        <v>-1.5922</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.3011</v>
+        <v>-0.5887</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0035</v>
+        <v>-1.0037</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.649800000000001</v>
+        <v>-5.6498</v>
       </c>
       <c r="W12" t="n">
         <v>3.6265</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1324</v>
+        <v>4.5004</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6975</v>
+        <v>3.2505</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4348</v>
+        <v>1.2499</v>
       </c>
       <c r="G13" t="n">
         <v>4.301</v>
@@ -1468,13 +1468,13 @@
         <v>1.5225</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4197</v>
+        <v>0.7877</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8172</v>
+        <v>0.3701</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6025</v>
+        <v>0.4176</v>
       </c>
       <c r="V13" t="n">
         <v>2.2393</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>D. MANCHON CRESPO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0422</v>
+        <v>3.1209</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3121</v>
+        <v>2.0475</v>
       </c>
       <c r="F14" t="n">
-        <v>5.3543</v>
+        <v>1.0734</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.061</v>
+        <v>3.3832</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9853</v>
+        <v>0.5321</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9243</v>
+        <v>2.8511</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.2267</v>
+        <v>3.4313</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.3415</v>
+        <v>0.3713</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1147</v>
+        <v>3.0599</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1658</v>
+        <v>-0.048</v>
       </c>
       <c r="N14" t="n">
-        <v>1.3562</v>
+        <v>0.1608</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8096</v>
+        <v>-0.2088</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2175</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R14" t="n">
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3652</v>
+        <v>0.0003</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4817</v>
+        <v>0.1839</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8835</v>
+        <v>-0.1836</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5204</v>
+        <v>1.695</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5204</v>
+        <v>1.695</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. AURRECOECHEA ALCOLADO</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2045</v>
+        <v>3.0114</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9441</v>
+        <v>-1.5415</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7396</v>
+        <v>4.5529</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2967</v>
+        <v>-0.061</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4385</v>
+        <v>-0.9853</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8582</v>
+        <v>0.9243</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0587</v>
+        <v>-2.2267</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7583</v>
+        <v>-2.3415</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3005</v>
+        <v>0.1147</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.762</v>
+        <v>2.1658</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3197</v>
+        <v>1.3562</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4423</v>
+        <v>0.8096</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7778</v>
+        <v>1.3345</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1703</v>
+        <v>0.2524</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6076</v>
+        <v>1.0821</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8902</v>
+        <v>1.5204</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. MANCHON CRESPO</t>
+          <t>I. AURRECOECHEA ALCOLADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6701</v>
+        <v>2.3201</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9357</v>
+        <v>3.4913</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7344000000000001</v>
+        <v>-1.1711</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3832</v>
+        <v>2.2967</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5321</v>
+        <v>1.4385</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8511</v>
+        <v>0.8582</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4313</v>
+        <v>3.0587</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3713</v>
+        <v>1.7583</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0599</v>
+        <v>1.3005</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.048</v>
+        <v>-0.762</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1608</v>
+        <v>-0.3197</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2088</v>
+        <v>-0.4423</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.9576</v>
+        <v>-0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4505</v>
+        <v>0.8935</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0721</v>
+        <v>0.7174</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5226</v>
+        <v>0.176</v>
       </c>
       <c r="V16" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.695</v>
+        <v>1.8902</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4509</v>
+        <v>1.0828</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1081</v>
+        <v>-0.6611</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5589</v>
+        <v>1.7439</v>
       </c>
       <c r="G17" t="n">
         <v>1.1856</v>
@@ -1780,13 +1780,13 @@
         <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7347</v>
+        <v>-0.1027</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4795</v>
+        <v>-0.0324</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2552</v>
+        <v>-0.0703</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RUPÉREZ VÁZQUEZ</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2175</v>
+        <v>0.2892</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-1.5403</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2175</v>
+        <v>1.8295</v>
       </c>
       <c r="G18" t="n">
-        <v>0.149</v>
+        <v>-0.1821</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.1701</v>
       </c>
       <c r="I18" t="n">
-        <v>0.149</v>
+        <v>-0.3522</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-1.3024</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.6721</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.6303</v>
       </c>
       <c r="M18" t="n">
-        <v>0.149</v>
+        <v>1.1203</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0.149</v>
+        <v>0.2781</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0565</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.2379</v>
       </c>
       <c r="U18" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.2944</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>A. RUPÉREZ VÁZQUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4044</v>
+        <v>0.2175</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9873</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5829</v>
+        <v>0.2175</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1821</v>
+        <v>0.149</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1701</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3522</v>
+        <v>0.149</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3024</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6721</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6303</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1203</v>
+        <v>0.149</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8421999999999999</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2781</v>
+        <v>0.149</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6371</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0478</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5504</v>
+        <v>-2.3288</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3205</v>
+        <v>-2.3147</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2299</v>
+        <v>-0.0141</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8343</v>
@@ -2014,13 +2014,13 @@
         <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1288</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.536</v>
+        <v>0.4699</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5928</v>
+        <v>-0.377</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9347</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4621</v>
+        <v>-4.2925</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.760400000000001</v>
+        <v>-8.3134</v>
       </c>
       <c r="F21" t="n">
-        <v>4.2983</v>
+        <v>4.0209</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2094</v>
@@ -2092,13 +2092,13 @@
         <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>0.315</v>
+        <v>0.4846</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9589</v>
+        <v>-0.5119</v>
       </c>
       <c r="U21" t="n">
-        <v>1.2739</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>1.13</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3608</v>
+        <v>-4.9813</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.5898</v>
+        <v>-5.9193</v>
       </c>
       <c r="F22" t="n">
-        <v>0.229</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0804</v>
@@ -2170,13 +2170,13 @@
         <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6904</v>
+        <v>-0.3109</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8784</v>
+        <v>-0.2079</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.1031</v>
       </c>
       <c r="V22" t="n">
         <v>1.3252</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.939899999999999</v>
+        <v>2.939699999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-11.5009</v>
+        <v>-11.501</v>
       </c>
       <c r="F23" t="n">
-        <v>14.4406</v>
+        <v>14.4408</v>
       </c>
       <c r="G23" t="n">
         <v>5.948299999999999</v>
@@ -2224,7 +2224,7 @@
         <v>3.232599999999998</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4691000000000003</v>
+        <v>-0.4690999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>3.7016</v>
@@ -2248,19 +2248,19 @@
         <v>13.0502</v>
       </c>
       <c r="S23" t="n">
-        <v>3.304700000000001</v>
+        <v>3.304799999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0035</v>
+        <v>1.0036</v>
       </c>
       <c r="U23" t="n">
-        <v>2.3012</v>
+        <v>2.3011</v>
       </c>
       <c r="V23" t="n">
-        <v>5.649999999999999</v>
+        <v>5.65</v>
       </c>
       <c r="W23" t="n">
-        <v>9.276400000000001</v>
+        <v>9.276399999999999</v>
       </c>
       <c r="X23" t="n">
         <v>-3.6266</v>
